--- a/templates/samples/INVENTORY_REPORT_SAMPLE.xlsx
+++ b/templates/samples/INVENTORY_REPORT_SAMPLE.xlsx
@@ -445,13 +445,13 @@
         <v>350100000000000</v>
       </c>
       <c r="D2" t="str">
-        <v>C</v>
+        <v>Brand new</v>
       </c>
       <c r="E2" t="str">
         <v>64GB</v>
       </c>
       <c r="F2" t="str">
-        <v>Dual SIM</v>
+        <v>Not Applicable</v>
       </c>
       <c r="G2" t="str">
         <v>GRAPHITE</v>
@@ -480,7 +480,7 @@
         <v>350100000007919</v>
       </c>
       <c r="D3" t="str">
-        <v>B</v>
+        <v>C</v>
       </c>
       <c r="E3" t="str">
         <v>128GB</v>
@@ -550,7 +550,7 @@
         <v>350100000023757</v>
       </c>
       <c r="D5" t="str">
-        <v>B</v>
+        <v>C</v>
       </c>
       <c r="E5" t="str">
         <v>256GB</v>
@@ -585,7 +585,7 @@
         <v>350100000031676</v>
       </c>
       <c r="D6" t="str">
-        <v>B</v>
+        <v>C</v>
       </c>
       <c r="E6" t="str">
         <v>256GB</v>
@@ -620,7 +620,7 @@
         <v>350100000039595</v>
       </c>
       <c r="D7" t="str">
-        <v>C</v>
+        <v>Brand new</v>
       </c>
       <c r="E7" t="str">
         <v>128GB</v>
@@ -655,13 +655,13 @@
         <v>350100000047514</v>
       </c>
       <c r="D8" t="str">
-        <v>B</v>
+        <v>C</v>
       </c>
       <c r="E8" t="str">
         <v>256GB</v>
       </c>
       <c r="F8" t="str">
-        <v>eSIM</v>
+        <v>Physical SIM + eSIM</v>
       </c>
       <c r="G8" t="str">
         <v>WHITE</v>
@@ -690,13 +690,13 @@
         <v>350100000055433</v>
       </c>
       <c r="D9" t="str">
-        <v>A+</v>
+        <v>B</v>
       </c>
       <c r="E9" t="str">
         <v>128GB</v>
       </c>
       <c r="F9" t="str">
-        <v>Dual SIM</v>
+        <v>Not Applicable</v>
       </c>
       <c r="G9" t="str">
         <v>WHITE</v>
@@ -725,7 +725,7 @@
         <v>350100000063352</v>
       </c>
       <c r="D10" t="str">
-        <v>C</v>
+        <v>Brand new</v>
       </c>
       <c r="E10" t="str">
         <v>64GB</v>
@@ -766,7 +766,7 @@
         <v>128GB</v>
       </c>
       <c r="F11" t="str">
-        <v>Dual SIM</v>
+        <v>Not Applicable</v>
       </c>
       <c r="G11" t="str">
         <v>WHITE</v>
@@ -801,7 +801,7 @@
         <v>128GB</v>
       </c>
       <c r="F12" t="str">
-        <v>Dual SIM</v>
+        <v>Not Applicable</v>
       </c>
       <c r="G12" t="str">
         <v>GREEN</v>
@@ -830,7 +830,7 @@
         <v>350100000087109</v>
       </c>
       <c r="D13" t="str">
-        <v>B</v>
+        <v>C</v>
       </c>
       <c r="E13" t="str">
         <v>256GB</v>
@@ -865,13 +865,13 @@
         <v>350100000095028</v>
       </c>
       <c r="D14" t="str">
-        <v>B+</v>
+        <v>ONU</v>
       </c>
       <c r="E14" t="str">
         <v>256GB</v>
       </c>
       <c r="F14" t="str">
-        <v>Dual SIM</v>
+        <v>Not Applicable</v>
       </c>
       <c r="G14" t="str">
         <v>MIDNIGHT</v>
@@ -935,13 +935,13 @@
         <v>350100000110866</v>
       </c>
       <c r="D16" t="str">
-        <v>C</v>
+        <v>Brand new</v>
       </c>
       <c r="E16" t="str">
         <v>256GB</v>
       </c>
       <c r="F16" t="str">
-        <v>Dual SIM</v>
+        <v>Not Applicable</v>
       </c>
       <c r="G16" t="str">
         <v>WHITE</v>
@@ -976,7 +976,7 @@
         <v>128GB</v>
       </c>
       <c r="F17" t="str">
-        <v>Dual SIM</v>
+        <v>Not Applicable</v>
       </c>
       <c r="G17" t="str">
         <v>BLACK</v>
@@ -1005,13 +1005,13 @@
         <v>350100000126704</v>
       </c>
       <c r="D18" t="str">
-        <v>A+</v>
+        <v>B</v>
       </c>
       <c r="E18" t="str">
         <v>64GB</v>
       </c>
       <c r="F18" t="str">
-        <v>Physical SIM</v>
+        <v>Physical SIM + eSIM</v>
       </c>
       <c r="G18" t="str">
         <v>MIDNIGHT</v>
@@ -1075,13 +1075,13 @@
         <v>350100000142542</v>
       </c>
       <c r="D20" t="str">
-        <v>C</v>
+        <v>Brand new</v>
       </c>
       <c r="E20" t="str">
         <v>128GB</v>
       </c>
       <c r="F20" t="str">
-        <v>Dual SIM</v>
+        <v>Not Applicable</v>
       </c>
       <c r="G20" t="str">
         <v>BLUE</v>
@@ -1110,13 +1110,13 @@
         <v>350100000150461</v>
       </c>
       <c r="D21" t="str">
-        <v>A+</v>
+        <v>B</v>
       </c>
       <c r="E21" t="str">
         <v>256GB</v>
       </c>
       <c r="F21" t="str">
-        <v>Dual SIM</v>
+        <v>Not Applicable</v>
       </c>
       <c r="G21" t="str">
         <v>GRAPHITE</v>
@@ -1145,13 +1145,13 @@
         <v>350100000158380</v>
       </c>
       <c r="D22" t="str">
-        <v>A+</v>
+        <v>B</v>
       </c>
       <c r="E22" t="str">
         <v>256GB</v>
       </c>
       <c r="F22" t="str">
-        <v>Dual SIM</v>
+        <v>Not Applicable</v>
       </c>
       <c r="G22" t="str">
         <v>GREEN</v>
@@ -1180,7 +1180,7 @@
         <v>350100000166299</v>
       </c>
       <c r="D23" t="str">
-        <v>B</v>
+        <v>C</v>
       </c>
       <c r="E23" t="str">
         <v>128GB</v>
@@ -1215,13 +1215,13 @@
         <v>350100000174218</v>
       </c>
       <c r="D24" t="str">
-        <v>A+</v>
+        <v>B</v>
       </c>
       <c r="E24" t="str">
         <v>256GB</v>
       </c>
       <c r="F24" t="str">
-        <v>Dual SIM</v>
+        <v>Not Applicable</v>
       </c>
       <c r="G24" t="str">
         <v>MIDNIGHT</v>
@@ -1250,13 +1250,13 @@
         <v>350100000182137</v>
       </c>
       <c r="D25" t="str">
-        <v>C</v>
+        <v>Brand new</v>
       </c>
       <c r="E25" t="str">
         <v>128GB</v>
       </c>
       <c r="F25" t="str">
-        <v>Dual SIM</v>
+        <v>Dual Physical SIM</v>
       </c>
       <c r="G25" t="str">
         <v>BLACK</v>
@@ -1285,13 +1285,13 @@
         <v>350100000190056</v>
       </c>
       <c r="D26" t="str">
-        <v>B+</v>
+        <v>ONU</v>
       </c>
       <c r="E26" t="str">
         <v>64GB</v>
       </c>
       <c r="F26" t="str">
-        <v>Dual SIM</v>
+        <v>Dual Physical SIM</v>
       </c>
       <c r="G26" t="str">
         <v>GRAPHITE</v>
@@ -1326,7 +1326,7 @@
         <v>128GB</v>
       </c>
       <c r="F27" t="str">
-        <v>Dual SIM</v>
+        <v>Not Applicable</v>
       </c>
       <c r="G27" t="str">
         <v>STARLIGHT</v>
@@ -1361,7 +1361,7 @@
         <v>128GB</v>
       </c>
       <c r="F28" t="str">
-        <v>Dual SIM</v>
+        <v>Dual Physical SIM</v>
       </c>
       <c r="G28" t="str">
         <v>PURPLE</v>
@@ -1390,13 +1390,13 @@
         <v>350100000213813</v>
       </c>
       <c r="D29" t="str">
-        <v>C</v>
+        <v>Brand new</v>
       </c>
       <c r="E29" t="str">
         <v>256GB</v>
       </c>
       <c r="F29" t="str">
-        <v>Dual SIM</v>
+        <v>Not Applicable</v>
       </c>
       <c r="G29" t="str">
         <v>MIDNIGHT</v>
@@ -1425,7 +1425,7 @@
         <v>350100000221732</v>
       </c>
       <c r="D30" t="str">
-        <v>B+</v>
+        <v>ONU</v>
       </c>
       <c r="E30" t="str">
         <v>256GB</v>
@@ -1460,7 +1460,7 @@
         <v>350100000229651</v>
       </c>
       <c r="D31" t="str">
-        <v>B</v>
+        <v>C</v>
       </c>
       <c r="E31" t="str">
         <v>128GB</v>
@@ -1530,7 +1530,7 @@
         <v>350100000245489</v>
       </c>
       <c r="D33" t="str">
-        <v>A+</v>
+        <v>B</v>
       </c>
       <c r="E33" t="str">
         <v>128GB</v>
@@ -1565,13 +1565,13 @@
         <v>350100000253408</v>
       </c>
       <c r="D34" t="str">
-        <v>B+</v>
+        <v>ONU</v>
       </c>
       <c r="E34" t="str">
         <v>64GB</v>
       </c>
       <c r="F34" t="str">
-        <v>Dual SIM</v>
+        <v>Dual Physical SIM</v>
       </c>
       <c r="G34" t="str">
         <v>GREEN</v>
@@ -1635,13 +1635,13 @@
         <v>350100000269246</v>
       </c>
       <c r="D36" t="str">
-        <v>C</v>
+        <v>Brand new</v>
       </c>
       <c r="E36" t="str">
         <v>128GB</v>
       </c>
       <c r="F36" t="str">
-        <v>Dual SIM</v>
+        <v>Not Applicable</v>
       </c>
       <c r="G36" t="str">
         <v>GREEN</v>
@@ -1670,13 +1670,13 @@
         <v>350100000277165</v>
       </c>
       <c r="D37" t="str">
-        <v>C</v>
+        <v>Brand new</v>
       </c>
       <c r="E37" t="str">
         <v>256GB</v>
       </c>
       <c r="F37" t="str">
-        <v>eSIM</v>
+        <v>Dual Physical SIM</v>
       </c>
       <c r="G37" t="str">
         <v>GREEN</v>
@@ -1705,13 +1705,13 @@
         <v>350100000285084</v>
       </c>
       <c r="D38" t="str">
-        <v>A+</v>
+        <v>B</v>
       </c>
       <c r="E38" t="str">
         <v>256GB</v>
       </c>
       <c r="F38" t="str">
-        <v>eSIM</v>
+        <v>Dual Physical SIM</v>
       </c>
       <c r="G38" t="str">
         <v>MIDNIGHT</v>
@@ -1746,7 +1746,7 @@
         <v>128GB</v>
       </c>
       <c r="F39" t="str">
-        <v>eSIM</v>
+        <v>Dual Physical SIM</v>
       </c>
       <c r="G39" t="str">
         <v>GREEN</v>
@@ -1781,7 +1781,7 @@
         <v>256GB</v>
       </c>
       <c r="F40" t="str">
-        <v>Dual SIM</v>
+        <v>Dual Physical SIM</v>
       </c>
       <c r="G40" t="str">
         <v>MIDNIGHT</v>
@@ -1810,7 +1810,7 @@
         <v>350100000308841</v>
       </c>
       <c r="D41" t="str">
-        <v>B</v>
+        <v>C</v>
       </c>
       <c r="E41" t="str">
         <v>128GB</v>
@@ -1845,7 +1845,7 @@
         <v>350100000316760</v>
       </c>
       <c r="D42" t="str">
-        <v>B+</v>
+        <v>ONU</v>
       </c>
       <c r="E42" t="str">
         <v>64GB</v>
@@ -1880,13 +1880,13 @@
         <v>350100000324679</v>
       </c>
       <c r="D43" t="str">
-        <v>B</v>
+        <v>C</v>
       </c>
       <c r="E43" t="str">
         <v>128GB</v>
       </c>
       <c r="F43" t="str">
-        <v>Dual SIM</v>
+        <v>Not Applicable</v>
       </c>
       <c r="G43" t="str">
         <v>MIDNIGHT</v>
@@ -1921,7 +1921,7 @@
         <v>128GB</v>
       </c>
       <c r="F44" t="str">
-        <v>Dual SIM</v>
+        <v>Not Applicable</v>
       </c>
       <c r="G44" t="str">
         <v>WHITE</v>
@@ -1950,13 +1950,13 @@
         <v>350100000340517</v>
       </c>
       <c r="D45" t="str">
-        <v>A+</v>
+        <v>B</v>
       </c>
       <c r="E45" t="str">
         <v>256GB</v>
       </c>
       <c r="F45" t="str">
-        <v>Dual SIM</v>
+        <v>Dual Physical SIM</v>
       </c>
       <c r="G45" t="str">
         <v>STARLIGHT</v>
@@ -2020,13 +2020,13 @@
         <v>350100000356355</v>
       </c>
       <c r="D47" t="str">
-        <v>B</v>
+        <v>C</v>
       </c>
       <c r="E47" t="str">
         <v>128GB</v>
       </c>
       <c r="F47" t="str">
-        <v>Dual SIM</v>
+        <v>Not Applicable</v>
       </c>
       <c r="G47" t="str">
         <v>MIDNIGHT</v>
@@ -2055,13 +2055,13 @@
         <v>350100000364274</v>
       </c>
       <c r="D48" t="str">
-        <v>B</v>
+        <v>C</v>
       </c>
       <c r="E48" t="str">
         <v>256GB</v>
       </c>
       <c r="F48" t="str">
-        <v>eSIM</v>
+        <v>Physical SIM + eSIM</v>
       </c>
       <c r="G48" t="str">
         <v>PURPLE</v>
@@ -2090,13 +2090,13 @@
         <v>350100000372193</v>
       </c>
       <c r="D49" t="str">
-        <v>C</v>
+        <v>Brand new</v>
       </c>
       <c r="E49" t="str">
         <v>128GB</v>
       </c>
       <c r="F49" t="str">
-        <v>Dual SIM</v>
+        <v>Not Applicable</v>
       </c>
       <c r="G49" t="str">
         <v>GRAPHITE</v>
@@ -2125,13 +2125,13 @@
         <v>350100000380112</v>
       </c>
       <c r="D50" t="str">
-        <v>B+</v>
+        <v>ONU</v>
       </c>
       <c r="E50" t="str">
         <v>64GB</v>
       </c>
       <c r="F50" t="str">
-        <v>Dual SIM</v>
+        <v>Dual Physical SIM</v>
       </c>
       <c r="G50" t="str">
         <v>STARLIGHT</v>
@@ -2166,7 +2166,7 @@
         <v>128GB</v>
       </c>
       <c r="F51" t="str">
-        <v>Dual SIM</v>
+        <v>Dual Physical SIM</v>
       </c>
       <c r="G51" t="str">
         <v>BLACK</v>
@@ -2201,7 +2201,7 @@
         <v>128GB</v>
       </c>
       <c r="F52" t="str">
-        <v>Dual SIM</v>
+        <v>Dual Physical SIM</v>
       </c>
       <c r="G52" t="str">
         <v>BLUE</v>
@@ -2230,7 +2230,7 @@
         <v>350100000403869</v>
       </c>
       <c r="D53" t="str">
-        <v>A+</v>
+        <v>B</v>
       </c>
       <c r="E53" t="str">
         <v>256GB</v>
@@ -2265,13 +2265,13 @@
         <v>350100000411788</v>
       </c>
       <c r="D54" t="str">
-        <v>C</v>
+        <v>Brand new</v>
       </c>
       <c r="E54" t="str">
         <v>256GB</v>
       </c>
       <c r="F54" t="str">
-        <v>eSIM</v>
+        <v>Dual Physical SIM</v>
       </c>
       <c r="G54" t="str">
         <v>PURPLE</v>
@@ -2300,13 +2300,13 @@
         <v>350100000419707</v>
       </c>
       <c r="D55" t="str">
-        <v>A+</v>
+        <v>B</v>
       </c>
       <c r="E55" t="str">
         <v>128GB</v>
       </c>
       <c r="F55" t="str">
-        <v>eSIM</v>
+        <v>Physical SIM + eSIM</v>
       </c>
       <c r="G55" t="str">
         <v>STARLIGHT</v>
@@ -2335,7 +2335,7 @@
         <v>350100000427626</v>
       </c>
       <c r="D56" t="str">
-        <v>B+</v>
+        <v>ONU</v>
       </c>
       <c r="E56" t="str">
         <v>256GB</v>
@@ -2370,13 +2370,13 @@
         <v>350100000435545</v>
       </c>
       <c r="D57" t="str">
-        <v>A+</v>
+        <v>B</v>
       </c>
       <c r="E57" t="str">
         <v>128GB</v>
       </c>
       <c r="F57" t="str">
-        <v>Dual SIM</v>
+        <v>Not Applicable</v>
       </c>
       <c r="G57" t="str">
         <v>MIDNIGHT</v>
@@ -2405,13 +2405,13 @@
         <v>350100000443464</v>
       </c>
       <c r="D58" t="str">
-        <v>A+</v>
+        <v>B</v>
       </c>
       <c r="E58" t="str">
         <v>64GB</v>
       </c>
       <c r="F58" t="str">
-        <v>Dual SIM</v>
+        <v>Not Applicable</v>
       </c>
       <c r="G58" t="str">
         <v>MIDNIGHT</v>
@@ -2440,13 +2440,13 @@
         <v>350100000451383</v>
       </c>
       <c r="D59" t="str">
-        <v>B+</v>
+        <v>ONU</v>
       </c>
       <c r="E59" t="str">
         <v>128GB</v>
       </c>
       <c r="F59" t="str">
-        <v>eSIM</v>
+        <v>Physical SIM + eSIM</v>
       </c>
       <c r="G59" t="str">
         <v>BLACK</v>
@@ -2475,13 +2475,13 @@
         <v>350100000459302</v>
       </c>
       <c r="D60" t="str">
-        <v>B+</v>
+        <v>ONU</v>
       </c>
       <c r="E60" t="str">
         <v>128GB</v>
       </c>
       <c r="F60" t="str">
-        <v>Dual SIM</v>
+        <v>Not Applicable</v>
       </c>
       <c r="G60" t="str">
         <v>WHITE</v>
@@ -2510,7 +2510,7 @@
         <v>350100000467221</v>
       </c>
       <c r="D61" t="str">
-        <v>A+</v>
+        <v>B</v>
       </c>
       <c r="E61" t="str">
         <v>256GB</v>
@@ -2545,7 +2545,7 @@
         <v>350100000475140</v>
       </c>
       <c r="D62" t="str">
-        <v>B</v>
+        <v>C</v>
       </c>
       <c r="E62" t="str">
         <v>256GB</v>
@@ -2580,13 +2580,13 @@
         <v>350100000483059</v>
       </c>
       <c r="D63" t="str">
-        <v>B</v>
+        <v>C</v>
       </c>
       <c r="E63" t="str">
         <v>128GB</v>
       </c>
       <c r="F63" t="str">
-        <v>eSIM</v>
+        <v>Dual Physical SIM</v>
       </c>
       <c r="G63" t="str">
         <v>WHITE</v>
@@ -2615,7 +2615,7 @@
         <v>350100000490978</v>
       </c>
       <c r="D64" t="str">
-        <v>B+</v>
+        <v>ONU</v>
       </c>
       <c r="E64" t="str">
         <v>256GB</v>
@@ -2650,13 +2650,13 @@
         <v>350100000498897</v>
       </c>
       <c r="D65" t="str">
-        <v>B+</v>
+        <v>ONU</v>
       </c>
       <c r="E65" t="str">
         <v>128GB</v>
       </c>
       <c r="F65" t="str">
-        <v>Dual SIM</v>
+        <v>Dual Physical SIM</v>
       </c>
       <c r="G65" t="str">
         <v>BLUE</v>
@@ -2685,7 +2685,7 @@
         <v>350100000506816</v>
       </c>
       <c r="D66" t="str">
-        <v>B+</v>
+        <v>ONU</v>
       </c>
       <c r="E66" t="str">
         <v>64GB</v>
@@ -2720,13 +2720,13 @@
         <v>350100000514735</v>
       </c>
       <c r="D67" t="str">
-        <v>B</v>
+        <v>C</v>
       </c>
       <c r="E67" t="str">
         <v>128GB</v>
       </c>
       <c r="F67" t="str">
-        <v>eSIM</v>
+        <v>Physical SIM + eSIM</v>
       </c>
       <c r="G67" t="str">
         <v>WHITE</v>
@@ -2755,13 +2755,13 @@
         <v>350100000522654</v>
       </c>
       <c r="D68" t="str">
-        <v>B</v>
+        <v>C</v>
       </c>
       <c r="E68" t="str">
         <v>128GB</v>
       </c>
       <c r="F68" t="str">
-        <v>Dual SIM</v>
+        <v>Dual Physical SIM</v>
       </c>
       <c r="G68" t="str">
         <v>BLACK</v>
@@ -2790,13 +2790,13 @@
         <v>350100000530573</v>
       </c>
       <c r="D69" t="str">
-        <v>C</v>
+        <v>Brand new</v>
       </c>
       <c r="E69" t="str">
         <v>256GB</v>
       </c>
       <c r="F69" t="str">
-        <v>Dual SIM</v>
+        <v>Dual Physical SIM</v>
       </c>
       <c r="G69" t="str">
         <v>GRAPHITE</v>
@@ -2825,7 +2825,7 @@
         <v>350100000538492</v>
       </c>
       <c r="D70" t="str">
-        <v>A+</v>
+        <v>B</v>
       </c>
       <c r="E70" t="str">
         <v>256GB</v>
@@ -2866,7 +2866,7 @@
         <v>128GB</v>
       </c>
       <c r="F71" t="str">
-        <v>Dual SIM</v>
+        <v>Not Applicable</v>
       </c>
       <c r="G71" t="str">
         <v>BLUE</v>
@@ -2895,13 +2895,13 @@
         <v>350100000554330</v>
       </c>
       <c r="D72" t="str">
-        <v>B+</v>
+        <v>ONU</v>
       </c>
       <c r="E72" t="str">
         <v>256GB</v>
       </c>
       <c r="F72" t="str">
-        <v>eSIM</v>
+        <v>Physical SIM + eSIM</v>
       </c>
       <c r="G72" t="str">
         <v>GRAPHITE</v>
@@ -2971,7 +2971,7 @@
         <v>64GB</v>
       </c>
       <c r="F74" t="str">
-        <v>Dual SIM</v>
+        <v>Not Applicable</v>
       </c>
       <c r="G74" t="str">
         <v>BLACK</v>
@@ -3000,13 +3000,13 @@
         <v>350100000578087</v>
       </c>
       <c r="D75" t="str">
-        <v>A+</v>
+        <v>B</v>
       </c>
       <c r="E75" t="str">
         <v>128GB</v>
       </c>
       <c r="F75" t="str">
-        <v>Dual SIM</v>
+        <v>Not Applicable</v>
       </c>
       <c r="G75" t="str">
         <v>MIDNIGHT</v>
@@ -3035,13 +3035,13 @@
         <v>350100000586006</v>
       </c>
       <c r="D76" t="str">
-        <v>A+</v>
+        <v>B</v>
       </c>
       <c r="E76" t="str">
         <v>128GB</v>
       </c>
       <c r="F76" t="str">
-        <v>eSIM</v>
+        <v>Dual Physical SIM</v>
       </c>
       <c r="G76" t="str">
         <v>PURPLE</v>
@@ -3070,13 +3070,13 @@
         <v>350100000593925</v>
       </c>
       <c r="D77" t="str">
-        <v>C</v>
+        <v>Brand new</v>
       </c>
       <c r="E77" t="str">
         <v>256GB</v>
       </c>
       <c r="F77" t="str">
-        <v>Physical SIM</v>
+        <v>Physical SIM + eSIM</v>
       </c>
       <c r="G77" t="str">
         <v>BLACK</v>
@@ -3105,13 +3105,13 @@
         <v>350100000601844</v>
       </c>
       <c r="D78" t="str">
-        <v>C</v>
+        <v>Brand new</v>
       </c>
       <c r="E78" t="str">
         <v>256GB</v>
       </c>
       <c r="F78" t="str">
-        <v>Physical SIM</v>
+        <v>Physical SIM + eSIM</v>
       </c>
       <c r="G78" t="str">
         <v>STARLIGHT</v>
@@ -3140,13 +3140,13 @@
         <v>350100000609763</v>
       </c>
       <c r="D79" t="str">
-        <v>A+</v>
+        <v>B</v>
       </c>
       <c r="E79" t="str">
         <v>128GB</v>
       </c>
       <c r="F79" t="str">
-        <v>eSIM</v>
+        <v>Physical SIM + eSIM</v>
       </c>
       <c r="G79" t="str">
         <v>WHITE</v>
@@ -3181,7 +3181,7 @@
         <v>256GB</v>
       </c>
       <c r="F80" t="str">
-        <v>Dual SIM</v>
+        <v>Dual Physical SIM</v>
       </c>
       <c r="G80" t="str">
         <v>GREEN</v>
@@ -3210,13 +3210,13 @@
         <v>350100000625601</v>
       </c>
       <c r="D81" t="str">
-        <v>B+</v>
+        <v>ONU</v>
       </c>
       <c r="E81" t="str">
         <v>128GB</v>
       </c>
       <c r="F81" t="str">
-        <v>Dual SIM</v>
+        <v>Not Applicable</v>
       </c>
       <c r="G81" t="str">
         <v>WHITE</v>
@@ -3245,7 +3245,7 @@
         <v>350100000633520</v>
       </c>
       <c r="D82" t="str">
-        <v>C</v>
+        <v>Brand new</v>
       </c>
       <c r="E82" t="str">
         <v>64GB</v>
@@ -3280,7 +3280,7 @@
         <v>350100000641439</v>
       </c>
       <c r="D83" t="str">
-        <v>C</v>
+        <v>Brand new</v>
       </c>
       <c r="E83" t="str">
         <v>128GB</v>
@@ -3321,7 +3321,7 @@
         <v>128GB</v>
       </c>
       <c r="F84" t="str">
-        <v>Dual SIM</v>
+        <v>Not Applicable</v>
       </c>
       <c r="G84" t="str">
         <v>MIDNIGHT</v>
@@ -3350,7 +3350,7 @@
         <v>350100000657277</v>
       </c>
       <c r="D85" t="str">
-        <v>B+</v>
+        <v>ONU</v>
       </c>
       <c r="E85" t="str">
         <v>256GB</v>
@@ -3385,13 +3385,13 @@
         <v>350100000665196</v>
       </c>
       <c r="D86" t="str">
-        <v>B+</v>
+        <v>ONU</v>
       </c>
       <c r="E86" t="str">
         <v>256GB</v>
       </c>
       <c r="F86" t="str">
-        <v>eSIM</v>
+        <v>Physical SIM + eSIM</v>
       </c>
       <c r="G86" t="str">
         <v>WHITE</v>
@@ -3426,7 +3426,7 @@
         <v>128GB</v>
       </c>
       <c r="F87" t="str">
-        <v>eSIM</v>
+        <v>Dual Physical SIM</v>
       </c>
       <c r="G87" t="str">
         <v>GRAPHITE</v>
@@ -3461,7 +3461,7 @@
         <v>256GB</v>
       </c>
       <c r="F88" t="str">
-        <v>Dual SIM</v>
+        <v>Not Applicable</v>
       </c>
       <c r="G88" t="str">
         <v>GRAPHITE</v>
@@ -3490,13 +3490,13 @@
         <v>350100000688953</v>
       </c>
       <c r="D89" t="str">
-        <v>B+</v>
+        <v>ONU</v>
       </c>
       <c r="E89" t="str">
         <v>128GB</v>
       </c>
       <c r="F89" t="str">
-        <v>eSIM</v>
+        <v>Physical SIM + eSIM</v>
       </c>
       <c r="G89" t="str">
         <v>STARLIGHT</v>
@@ -3525,13 +3525,13 @@
         <v>350100000696872</v>
       </c>
       <c r="D90" t="str">
-        <v>B</v>
+        <v>C</v>
       </c>
       <c r="E90" t="str">
         <v>64GB</v>
       </c>
       <c r="F90" t="str">
-        <v>eSIM</v>
+        <v>Dual Physical SIM</v>
       </c>
       <c r="G90" t="str">
         <v>STARLIGHT</v>
@@ -3595,13 +3595,13 @@
         <v>350100000712710</v>
       </c>
       <c r="D92" t="str">
-        <v>B</v>
+        <v>C</v>
       </c>
       <c r="E92" t="str">
         <v>128GB</v>
       </c>
       <c r="F92" t="str">
-        <v>eSIM</v>
+        <v>Physical SIM + eSIM</v>
       </c>
       <c r="G92" t="str">
         <v>GRAPHITE</v>
@@ -3630,7 +3630,7 @@
         <v>350100000720629</v>
       </c>
       <c r="D93" t="str">
-        <v>B</v>
+        <v>C</v>
       </c>
       <c r="E93" t="str">
         <v>256GB</v>
@@ -3665,13 +3665,13 @@
         <v>350100000728548</v>
       </c>
       <c r="D94" t="str">
-        <v>C</v>
+        <v>Brand new</v>
       </c>
       <c r="E94" t="str">
         <v>256GB</v>
       </c>
       <c r="F94" t="str">
-        <v>eSIM</v>
+        <v>Physical SIM + eSIM</v>
       </c>
       <c r="G94" t="str">
         <v>GRAPHITE</v>
@@ -3735,13 +3735,13 @@
         <v>350100000744386</v>
       </c>
       <c r="D96" t="str">
-        <v>B</v>
+        <v>C</v>
       </c>
       <c r="E96" t="str">
         <v>256GB</v>
       </c>
       <c r="F96" t="str">
-        <v>Dual SIM</v>
+        <v>Not Applicable</v>
       </c>
       <c r="G96" t="str">
         <v>PURPLE</v>
@@ -3770,13 +3770,13 @@
         <v>350100000752305</v>
       </c>
       <c r="D97" t="str">
-        <v>B</v>
+        <v>C</v>
       </c>
       <c r="E97" t="str">
         <v>128GB</v>
       </c>
       <c r="F97" t="str">
-        <v>Dual SIM</v>
+        <v>Not Applicable</v>
       </c>
       <c r="G97" t="str">
         <v>BLUE</v>
@@ -3840,13 +3840,13 @@
         <v>350100000768143</v>
       </c>
       <c r="D99" t="str">
-        <v>B+</v>
+        <v>ONU</v>
       </c>
       <c r="E99" t="str">
         <v>128GB</v>
       </c>
       <c r="F99" t="str">
-        <v>eSIM</v>
+        <v>Dual Physical SIM</v>
       </c>
       <c r="G99" t="str">
         <v>GRAPHITE</v>
@@ -3875,13 +3875,13 @@
         <v>350100000776062</v>
       </c>
       <c r="D100" t="str">
-        <v>A+</v>
+        <v>B</v>
       </c>
       <c r="E100" t="str">
         <v>128GB</v>
       </c>
       <c r="F100" t="str">
-        <v>Dual SIM</v>
+        <v>Not Applicable</v>
       </c>
       <c r="G100" t="str">
         <v>BLACK</v>
@@ -3910,13 +3910,13 @@
         <v>350100000783981</v>
       </c>
       <c r="D101" t="str">
-        <v>A+</v>
+        <v>B</v>
       </c>
       <c r="E101" t="str">
         <v>256GB</v>
       </c>
       <c r="F101" t="str">
-        <v>Dual SIM</v>
+        <v>Not Applicable</v>
       </c>
       <c r="G101" t="str">
         <v>BLACK</v>
@@ -3945,13 +3945,13 @@
         <v>350100000791900</v>
       </c>
       <c r="D102" t="str">
-        <v>C</v>
+        <v>Brand new</v>
       </c>
       <c r="E102" t="str">
         <v>256GB</v>
       </c>
       <c r="F102" t="str">
-        <v>Dual SIM</v>
+        <v>Not Applicable</v>
       </c>
       <c r="G102" t="str">
         <v>MIDNIGHT</v>
@@ -3980,13 +3980,13 @@
         <v>350100000799819</v>
       </c>
       <c r="D103" t="str">
-        <v>B+</v>
+        <v>ONU</v>
       </c>
       <c r="E103" t="str">
         <v>128GB</v>
       </c>
       <c r="F103" t="str">
-        <v>eSIM</v>
+        <v>Physical SIM + eSIM</v>
       </c>
       <c r="G103" t="str">
         <v>BLUE</v>
@@ -4085,13 +4085,13 @@
         <v>350100000823576</v>
       </c>
       <c r="D106" t="str">
-        <v>C</v>
+        <v>Brand new</v>
       </c>
       <c r="E106" t="str">
         <v>64GB</v>
       </c>
       <c r="F106" t="str">
-        <v>eSIM</v>
+        <v>Physical SIM + eSIM</v>
       </c>
       <c r="G106" t="str">
         <v>BLACK</v>
@@ -4120,7 +4120,7 @@
         <v>350100000831495</v>
       </c>
       <c r="D107" t="str">
-        <v>C</v>
+        <v>Brand new</v>
       </c>
       <c r="E107" t="str">
         <v>128GB</v>
@@ -4155,13 +4155,13 @@
         <v>350100000839414</v>
       </c>
       <c r="D108" t="str">
-        <v>C</v>
+        <v>Brand new</v>
       </c>
       <c r="E108" t="str">
         <v>128GB</v>
       </c>
       <c r="F108" t="str">
-        <v>eSIM</v>
+        <v>Dual Physical SIM</v>
       </c>
       <c r="G108" t="str">
         <v>WHITE</v>
@@ -4190,13 +4190,13 @@
         <v>350100000847333</v>
       </c>
       <c r="D109" t="str">
-        <v>B+</v>
+        <v>ONU</v>
       </c>
       <c r="E109" t="str">
         <v>256GB</v>
       </c>
       <c r="F109" t="str">
-        <v>eSIM</v>
+        <v>Physical SIM + eSIM</v>
       </c>
       <c r="G109" t="str">
         <v>BLUE</v>
@@ -4260,13 +4260,13 @@
         <v>350100000863171</v>
       </c>
       <c r="D111" t="str">
-        <v>C</v>
+        <v>Brand new</v>
       </c>
       <c r="E111" t="str">
         <v>128GB</v>
       </c>
       <c r="F111" t="str">
-        <v>Dual SIM</v>
+        <v>Dual Physical SIM</v>
       </c>
       <c r="G111" t="str">
         <v>BLUE</v>
@@ -4295,13 +4295,13 @@
         <v>350100000871090</v>
       </c>
       <c r="D112" t="str">
-        <v>C</v>
+        <v>Brand new</v>
       </c>
       <c r="E112" t="str">
         <v>256GB</v>
       </c>
       <c r="F112" t="str">
-        <v>eSIM</v>
+        <v>Dual Physical SIM</v>
       </c>
       <c r="G112" t="str">
         <v>STARLIGHT</v>
@@ -4330,13 +4330,13 @@
         <v>350100000879009</v>
       </c>
       <c r="D113" t="str">
-        <v>B+</v>
+        <v>ONU</v>
       </c>
       <c r="E113" t="str">
         <v>128GB</v>
       </c>
       <c r="F113" t="str">
-        <v>eSIM</v>
+        <v>Physical SIM + eSIM</v>
       </c>
       <c r="G113" t="str">
         <v>GRAPHITE</v>
@@ -4365,7 +4365,7 @@
         <v>350100000886928</v>
       </c>
       <c r="D114" t="str">
-        <v>B</v>
+        <v>C</v>
       </c>
       <c r="E114" t="str">
         <v>64GB</v>
@@ -4400,13 +4400,13 @@
         <v>350100000894847</v>
       </c>
       <c r="D115" t="str">
-        <v>B+</v>
+        <v>ONU</v>
       </c>
       <c r="E115" t="str">
         <v>128GB</v>
       </c>
       <c r="F115" t="str">
-        <v>eSIM</v>
+        <v>Physical SIM + eSIM</v>
       </c>
       <c r="G115" t="str">
         <v>STARLIGHT</v>
@@ -4435,13 +4435,13 @@
         <v>350100000902766</v>
       </c>
       <c r="D116" t="str">
-        <v>B+</v>
+        <v>ONU</v>
       </c>
       <c r="E116" t="str">
         <v>128GB</v>
       </c>
       <c r="F116" t="str">
-        <v>eSIM</v>
+        <v>Physical SIM + eSIM</v>
       </c>
       <c r="G116" t="str">
         <v>GREEN</v>
@@ -4470,7 +4470,7 @@
         <v>350100000910685</v>
       </c>
       <c r="D117" t="str">
-        <v>B+</v>
+        <v>ONU</v>
       </c>
       <c r="E117" t="str">
         <v>256GB</v>
@@ -4505,13 +4505,13 @@
         <v>350100000918604</v>
       </c>
       <c r="D118" t="str">
-        <v>B+</v>
+        <v>ONU</v>
       </c>
       <c r="E118" t="str">
         <v>256GB</v>
       </c>
       <c r="F118" t="str">
-        <v>Dual SIM</v>
+        <v>Not Applicable</v>
       </c>
       <c r="G118" t="str">
         <v>PURPLE</v>
@@ -4546,7 +4546,7 @@
         <v>128GB</v>
       </c>
       <c r="F119" t="str">
-        <v>Physical SIM</v>
+        <v>Physical SIM + eSIM</v>
       </c>
       <c r="G119" t="str">
         <v>WHITE</v>
@@ -4581,7 +4581,7 @@
         <v>256GB</v>
       </c>
       <c r="F120" t="str">
-        <v>eSIM</v>
+        <v>Physical SIM + eSIM</v>
       </c>
       <c r="G120" t="str">
         <v>GRAPHITE</v>
@@ -4610,13 +4610,13 @@
         <v>350100000942361</v>
       </c>
       <c r="D121" t="str">
-        <v>C</v>
+        <v>Brand new</v>
       </c>
       <c r="E121" t="str">
         <v>128GB</v>
       </c>
       <c r="F121" t="str">
-        <v>eSIM</v>
+        <v>Dual Physical SIM</v>
       </c>
       <c r="G121" t="str">
         <v>GRAPHITE</v>

--- a/templates/samples/INVENTORY_REPORT_SAMPLE.xlsx
+++ b/templates/samples/INVENTORY_REPORT_SAMPLE.xlsx
@@ -442,7 +442,7 @@
         <v>IPHONE 12</v>
       </c>
       <c r="C2" t="str">
-        <v>350100000000000</v>
+        <v/>
       </c>
       <c r="D2" t="str">
         <v>Brand new</v>
@@ -862,7 +862,7 @@
         <v>IPHONE 14</v>
       </c>
       <c r="C14" t="str">
-        <v>350100000095028</v>
+        <v/>
       </c>
       <c r="D14" t="str">
         <v>ONU</v>
@@ -1282,7 +1282,7 @@
         <v>IPHONE 12</v>
       </c>
       <c r="C26" t="str">
-        <v>350100000190056</v>
+        <v/>
       </c>
       <c r="D26" t="str">
         <v>ONU</v>
@@ -1702,7 +1702,7 @@
         <v>IPHONE 14</v>
       </c>
       <c r="C38" t="str">
-        <v>350100000285084</v>
+        <v/>
       </c>
       <c r="D38" t="str">
         <v>B</v>
@@ -2122,7 +2122,7 @@
         <v>IPHONE 12</v>
       </c>
       <c r="C50" t="str">
-        <v>350100000380112</v>
+        <v/>
       </c>
       <c r="D50" t="str">
         <v>ONU</v>
@@ -2542,7 +2542,7 @@
         <v>IPHONE 14</v>
       </c>
       <c r="C62" t="str">
-        <v>350100000475140</v>
+        <v/>
       </c>
       <c r="D62" t="str">
         <v>C</v>
@@ -2962,7 +2962,7 @@
         <v>IPHONE 12</v>
       </c>
       <c r="C74" t="str">
-        <v>350100000570168</v>
+        <v/>
       </c>
       <c r="D74" t="str">
         <v>A</v>
@@ -3382,7 +3382,7 @@
         <v>IPHONE 14</v>
       </c>
       <c r="C86" t="str">
-        <v>350100000665196</v>
+        <v/>
       </c>
       <c r="D86" t="str">
         <v>ONU</v>
@@ -3802,7 +3802,7 @@
         <v>IPHONE 12</v>
       </c>
       <c r="C98" t="str">
-        <v>350100000760224</v>
+        <v/>
       </c>
       <c r="D98" t="str">
         <v>A</v>
@@ -4222,7 +4222,7 @@
         <v>IPHONE 14</v>
       </c>
       <c r="C110" t="str">
-        <v>350100000855252</v>
+        <v/>
       </c>
       <c r="D110" t="str">
         <v>A</v>
